--- a/ig/nr-add-sato2-profile/ValueSet-method-glucose-vs.xlsx
+++ b/ig/nr-add-sato2-profile/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:33:27+00:00</t>
+    <t>2023-11-17T15:40:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-sato2-profile/ValueSet-method-glucose-vs.xlsx
+++ b/ig/nr-add-sato2-profile/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:40:40+00:00</t>
+    <t>2023-11-23T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
